--- a/reference-model/sample-inputs/lookups.xlsx
+++ b/reference-model/sample-inputs/lookups.xlsx
@@ -3,11 +3,6 @@
 <x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aa_git_repos\cassandra\cassandra_main\JCass_UnitTests\test_data\cassandra-unit-test-web\inputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1EDCC7-147B-4533-BD53-AB67DD346364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="-90" yWindow="0" windowWidth="25780" windowHeight="20970" firstSheet="0" activeTab="0" xr2:uid="{399D8ED1-DF05-4A41-ABD1-63947F661167}"/>
